--- a/Outputs/Scenarios/PtX_demand_AT_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_AT_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.00414387072335156</v>
       </c>
       <c r="K16" t="n">
-        <v>5.939903131894513e-05</v>
+        <v>0.0001385977397442053</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>9.899838553157521e-05</v>
+        <v>4.15793219232616e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1370,7 +1370,7 @@
         <v>0.002010144934382977</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0007784721901564351</v>
+        <v>0.0007784721901564352</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>5.970616272678076e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>3.959935421263009e-05</v>
+        <v>1.781970939568355e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.006134496104582772</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0002973926360801465</v>
+        <v>0.0006939161508536751</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0004956543934669107</v>
+        <v>0.0002081748452561026</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0003228682160306722</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0001982617573867643</v>
+        <v>8.921779082404396e-05</v>
       </c>
     </row>
     <row r="43">
